--- a/campaign/config/column_master.xlsx
+++ b/campaign/config/column_master.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24960" windowHeight="12120"/>
+    <workbookView windowWidth="28840" windowHeight="12120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
   <si>
     <t>sms_format</t>
   </si>
@@ -35,7 +35,7 @@
     <t>email_format</t>
   </si>
   <si>
-    <t>id</t>
+    <t>customer_ref_no</t>
   </si>
   <si>
     <t>first_name</t>
@@ -44,6 +44,9 @@
     <t>last_name</t>
   </si>
   <si>
+    <t>phone</t>
+  </si>
+  <si>
     <t>email</t>
   </si>
   <si>
@@ -57,6 +60,36 @@
   </si>
   <si>
     <t>analyst_email</t>
+  </si>
+  <si>
+    <t>execution_type</t>
+  </si>
+  <si>
+    <t>template_id</t>
+  </si>
+  <si>
+    <t>campaign_id</t>
+  </si>
+  <si>
+    <t>segment_id</t>
+  </si>
+  <si>
+    <t>campaign_name</t>
+  </si>
+  <si>
+    <t>campaign_execution_count</t>
+  </si>
+  <si>
+    <t>product_pitched</t>
+  </si>
+  <si>
+    <t>campaign_type</t>
+  </si>
+  <si>
+    <t>channel</t>
+  </si>
+  <si>
+    <t>exclusion_rule</t>
   </si>
 </sst>
 </file>
@@ -69,10 +102,16 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -542,139 +581,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1209,10 +1254,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="2" width="14.5625" customWidth="1"/>
+    <col min="1" max="1" width="24.5625" customWidth="1"/>
+    <col min="2" max="2" width="14.5625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1224,67 +1270,144 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" ht="17" spans="2:2">
+      <c r="B19" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/campaign/config/column_master.xlsx
+++ b/campaign/config/column_master.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>sms_format</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>exclusion_rule</t>
+  </si>
+  <si>
+    <t>contact_source</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1257,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="24.5625" customWidth="1"/>
@@ -1410,6 +1413,11 @@
         <v>20</v>
       </c>
     </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
